--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>10.56431666751386</v>
+        <v>1.716701458471003</v>
       </c>
       <c r="D2" t="n">
-        <v>10.43247670597145</v>
+        <v>1.69527746472036</v>
       </c>
       <c r="E2" t="n">
-        <v>14.39205859973491</v>
+        <v>2.338709522456923</v>
       </c>
       <c r="F2" t="n">
-        <v>13.19296026090464</v>
+        <v>2.143856042397004</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>30.06798324629529</v>
+        <v>4.886047277522985</v>
       </c>
       <c r="D3" t="n">
-        <v>32.09399151591139</v>
+        <v>5.215273621335601</v>
       </c>
       <c r="E3" t="n">
-        <v>14.39205859973491</v>
+        <v>2.338709522456923</v>
       </c>
       <c r="F3" t="n">
-        <v>13.19296026090464</v>
+        <v>2.143856042397004</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>15.44573036998513</v>
+        <v>2.509931185122583</v>
       </c>
       <c r="D4" t="n">
-        <v>5.529998635371789</v>
+        <v>0.8986247782479158</v>
       </c>
       <c r="E4" t="n">
-        <v>14.39205859973491</v>
+        <v>2.338709522456923</v>
       </c>
       <c r="F4" t="n">
-        <v>13.19296026090464</v>
+        <v>2.143856042397004</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.57153262640852</v>
+        <v>3.505374051791384</v>
       </c>
       <c r="D5" t="n">
-        <v>23.86219949916013</v>
+        <v>3.877607418613521</v>
       </c>
       <c r="E5" t="n">
-        <v>14.39205859973491</v>
+        <v>2.338709522456923</v>
       </c>
       <c r="F5" t="n">
-        <v>13.19296026090464</v>
+        <v>2.143856042397004</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>12.16921495193481</v>
+        <v>1.977497429689407</v>
       </c>
       <c r="D6" t="n">
-        <v>32.12804914066699</v>
+        <v>5.220807985358386</v>
       </c>
       <c r="E6" t="n">
-        <v>14.39205859973491</v>
+        <v>2.338709522456923</v>
       </c>
       <c r="F6" t="n">
-        <v>13.19296026090464</v>
+        <v>2.143856042397004</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>17.15551539427008</v>
+        <v>2.787771251568889</v>
       </c>
       <c r="D7" t="n">
-        <v>16.79470523778476</v>
+        <v>2.729139601140023</v>
       </c>
       <c r="E7" t="n">
-        <v>14.39205859973491</v>
+        <v>2.338709522456923</v>
       </c>
       <c r="F7" t="n">
-        <v>13.19296026090464</v>
+        <v>2.143856042397004</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>14.56318947749008</v>
+        <v>2.366518290092139</v>
       </c>
       <c r="D8" t="n">
-        <v>12.51605319429749</v>
+        <v>2.033858644073342</v>
       </c>
       <c r="E8" t="n">
-        <v>14.39205859973491</v>
+        <v>2.338709522456923</v>
       </c>
       <c r="F8" t="n">
-        <v>13.19296026090464</v>
+        <v>2.143856042397004</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>24.88903528068623</v>
+        <v>4.044468233111512</v>
       </c>
       <c r="D9" t="n">
-        <v>29.52113454525163</v>
+        <v>4.79718436360339</v>
       </c>
       <c r="E9" t="n">
-        <v>14.39205859973491</v>
+        <v>2.338709522456923</v>
       </c>
       <c r="F9" t="n">
-        <v>13.19296026090464</v>
+        <v>2.143856042397004</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>6.58547407667049</v>
+        <v>1.070139537458955</v>
       </c>
       <c r="D10" t="n">
-        <v>14.96671170567405</v>
+        <v>2.432090652172033</v>
       </c>
       <c r="E10" t="n">
-        <v>14.39205859973491</v>
+        <v>2.338709522456923</v>
       </c>
       <c r="F10" t="n">
-        <v>13.19296026090464</v>
+        <v>2.143856042397004</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>25.91473290475544</v>
+        <v>4.211144097022759</v>
       </c>
       <c r="D11" t="n">
-        <v>24.48395737347007</v>
+        <v>3.978643073188886</v>
       </c>
       <c r="E11" t="n">
-        <v>14.39205859973491</v>
+        <v>2.338709522456923</v>
       </c>
       <c r="F11" t="n">
-        <v>13.19296026090464</v>
+        <v>2.143856042397004</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>11.73538665104152</v>
+        <v>1.907000330794247</v>
       </c>
       <c r="D12" t="n">
-        <v>14.56035504026409</v>
+        <v>2.366057694042915</v>
       </c>
       <c r="E12" t="n">
-        <v>14.39205859973491</v>
+        <v>2.338709522456923</v>
       </c>
       <c r="F12" t="n">
-        <v>13.19296026090464</v>
+        <v>2.143856042397004</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>21.43792071177717</v>
+        <v>3.48366211566379</v>
       </c>
       <c r="D13" t="n">
-        <v>22.29224921442283</v>
+        <v>3.62249049734371</v>
       </c>
       <c r="E13" t="n">
-        <v>14.39205859973491</v>
+        <v>2.338709522456923</v>
       </c>
       <c r="F13" t="n">
-        <v>13.19296026090464</v>
+        <v>2.143856042397004</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>26.50586748039041</v>
+        <v>4.307203465563441</v>
       </c>
       <c r="D14" t="n">
-        <v>13.67009295118345</v>
+        <v>2.22139010456731</v>
       </c>
       <c r="E14" t="n">
-        <v>14.39205859973491</v>
+        <v>2.338709522456923</v>
       </c>
       <c r="F14" t="n">
-        <v>13.19296026090464</v>
+        <v>2.143856042397004</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>8.755039198889749</v>
+        <v>1.422693869819584</v>
       </c>
       <c r="D15" t="n">
-        <v>19.66744627880093</v>
+        <v>3.195960020305151</v>
       </c>
       <c r="E15" t="n">
-        <v>14.39205859973491</v>
+        <v>2.338709522456923</v>
       </c>
       <c r="F15" t="n">
-        <v>13.19296026090464</v>
+        <v>2.143856042397004</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>31.88074593281587</v>
+        <v>5.180621214082579</v>
       </c>
       <c r="D16" t="n">
-        <v>7.415389963044798</v>
+        <v>1.20500086899478</v>
       </c>
       <c r="E16" t="n">
-        <v>14.39205859973491</v>
+        <v>2.338709522456923</v>
       </c>
       <c r="F16" t="n">
-        <v>13.19296026090464</v>
+        <v>2.143856042397004</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>14.71393896956216</v>
+        <v>2.391015082553851</v>
       </c>
       <c r="D17" t="n">
-        <v>25.53014809080554</v>
+        <v>4.148649064755901</v>
       </c>
       <c r="E17" t="n">
-        <v>14.39205859973491</v>
+        <v>2.338709522456923</v>
       </c>
       <c r="F17" t="n">
-        <v>13.19296026090464</v>
+        <v>2.143856042397004</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>12.85294329023485</v>
+        <v>2.088603284663164</v>
       </c>
       <c r="D18" t="n">
-        <v>16.2347996168071</v>
+        <v>2.638154937731154</v>
       </c>
       <c r="E18" t="n">
-        <v>14.39205859973491</v>
+        <v>2.338709522456923</v>
       </c>
       <c r="F18" t="n">
-        <v>13.19296026090464</v>
+        <v>2.143856042397004</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>41.23203835895016</v>
+        <v>6.700206233329401</v>
       </c>
       <c r="D19" t="n">
-        <v>21.15427615377483</v>
+        <v>3.43756987498841</v>
       </c>
       <c r="E19" t="n">
-        <v>14.39205859973491</v>
+        <v>2.338709522456923</v>
       </c>
       <c r="F19" t="n">
-        <v>13.19296026090464</v>
+        <v>2.143856042397004</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>14.11476174648172</v>
+        <v>2.29364878380328</v>
       </c>
       <c r="D20" t="n">
-        <v>16.38506545938014</v>
+        <v>2.662573137149272</v>
       </c>
       <c r="E20" t="n">
-        <v>14.39205859973491</v>
+        <v>2.338709522456923</v>
       </c>
       <c r="F20" t="n">
-        <v>13.19296026090464</v>
+        <v>2.143856042397004</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>13.29473461742275</v>
+        <v>2.160394375331196</v>
       </c>
       <c r="D21" t="n">
-        <v>14.23905966239984</v>
+        <v>2.313847195139974</v>
       </c>
       <c r="E21" t="n">
-        <v>14.39205859973491</v>
+        <v>2.338709522456923</v>
       </c>
       <c r="F21" t="n">
-        <v>13.19296026090464</v>
+        <v>2.143856042397004</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>37.78285441194254</v>
+        <v>6.139713841940663</v>
       </c>
       <c r="D22" t="n">
-        <v>36.84126497696266</v>
+        <v>5.986705558756433</v>
       </c>
       <c r="E22" t="n">
-        <v>14.39205859973491</v>
+        <v>2.338709522456923</v>
       </c>
       <c r="F22" t="n">
-        <v>13.19296026090464</v>
+        <v>2.143856042397004</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>32.23030677885139</v>
+        <v>5.237424851563351</v>
       </c>
       <c r="D23" t="n">
-        <v>29.51989150758827</v>
+        <v>4.796982369983094</v>
       </c>
       <c r="E23" t="n">
-        <v>14.39205859973491</v>
+        <v>2.338709522456923</v>
       </c>
       <c r="F23" t="n">
-        <v>13.19296026090464</v>
+        <v>2.143856042397004</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>31.63038865438728</v>
+        <v>5.139938156337934</v>
       </c>
       <c r="D24" t="n">
-        <v>33.2463767892684</v>
+        <v>5.402536228256115</v>
       </c>
       <c r="E24" t="n">
-        <v>14.39205859973491</v>
+        <v>2.338709522456923</v>
       </c>
       <c r="F24" t="n">
-        <v>13.19296026090464</v>
+        <v>2.143856042397004</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>30.82448078333291</v>
+        <v>5.008978127291599</v>
       </c>
       <c r="D25" t="n">
-        <v>30.44918810220592</v>
+        <v>4.947993066608463</v>
       </c>
       <c r="E25" t="n">
-        <v>14.39205859973491</v>
+        <v>2.338709522456923</v>
       </c>
       <c r="F25" t="n">
-        <v>13.19296026090464</v>
+        <v>2.143856042397004</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>30.88518604289321</v>
+        <v>5.018842731970147</v>
       </c>
       <c r="D26" t="n">
-        <v>28.75088200635111</v>
+        <v>4.672018326032056</v>
       </c>
       <c r="E26" t="n">
-        <v>14.39205859973491</v>
+        <v>2.338709522456923</v>
       </c>
       <c r="F26" t="n">
-        <v>13.19296026090464</v>
+        <v>2.143856042397004</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>42.39799403415896</v>
+        <v>6.889674030550831</v>
       </c>
       <c r="D27" t="n">
-        <v>39.65706416946941</v>
+        <v>6.444272927538779</v>
       </c>
       <c r="E27" t="n">
-        <v>14.39205859973491</v>
+        <v>2.338709522456923</v>
       </c>
       <c r="F27" t="n">
-        <v>13.19296026090464</v>
+        <v>2.143856042397004</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>57.81148713144687</v>
+        <v>9.394366658860118</v>
       </c>
       <c r="D28" t="n">
-        <v>55.07345736661604</v>
+        <v>8.949436822075107</v>
       </c>
       <c r="E28" t="n">
-        <v>14.39205859973491</v>
+        <v>2.338709522456923</v>
       </c>
       <c r="F28" t="n">
-        <v>13.19296026090464</v>
+        <v>2.143856042397004</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>67.509772442212</v>
+        <v>10.97033802185945</v>
       </c>
       <c r="D29" t="n">
-        <v>64.7711954098146</v>
+        <v>10.52531925409487</v>
       </c>
       <c r="E29" t="n">
-        <v>14.39205859973491</v>
+        <v>2.338709522456923</v>
       </c>
       <c r="F29" t="n">
-        <v>13.19296026090464</v>
+        <v>2.143856042397004</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
